--- a/scripts/eeg/subjects_processing_stage.xlsx
+++ b/scripts/eeg/subjects_processing_stage.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahm\projects\loc_analysis\scripts\eeg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532F6943-4D52-4DD5-8286-1100288F3C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD579A5-9A2E-47EA-8225-13E1F5897BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="all_subjects" sheetId="1" r:id="rId1"/>
+    <sheet name="beh_incl_subjects" sheetId="4" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">beh_incl_subjects!$A$1:$G$30</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,10 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Subjects EEG processing stage</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="13">
   <si>
     <t>sub</t>
   </si>
@@ -44,15 +45,46 @@
   <si>
     <t>stage</t>
   </si>
+  <si>
+    <t>perfect</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>1: BIDS</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>2: manual config</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>PSD plots very noisy</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,15 +98,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -82,25 +120,484 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCCC"/>
+      <color rgb="FFFF7C80"/>
+      <color rgb="FFFF9999"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -375,502 +872,1173 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="A3" s="2">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B4" s="2">
-        <v>3</v>
+      <c r="B4" s="3">
+        <v>1</v>
       </c>
       <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B5" s="2">
-        <v>4</v>
+      <c r="A5" s="2">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B6" s="2">
-        <v>5</v>
+      <c r="A6" s="2">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B7" s="2">
+      <c r="A7" s="2">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B8" s="2">
-        <v>7</v>
+      <c r="A8" s="2">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B9" s="2">
-        <v>8</v>
+      <c r="A9" s="2">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B10" s="2">
-        <v>9</v>
+      <c r="A10" s="2">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0</v>
       </c>
       <c r="C10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B11" s="2">
-        <v>10</v>
+      <c r="A11" s="2">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
       </c>
       <c r="C11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B12" s="2">
-        <v>11</v>
+      <c r="A12" s="2">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
       </c>
       <c r="C12" s="3">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B13" s="2">
-        <v>12</v>
+      <c r="A13" s="2">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
       </c>
       <c r="C13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B14" s="2">
-        <v>13</v>
+      <c r="A14" s="2">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B15" s="2">
-        <v>14</v>
+      <c r="A15" s="2">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
       </c>
       <c r="C15" s="3">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B16" s="2">
-        <v>15</v>
+      <c r="A16" s="2">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0</v>
       </c>
       <c r="C16" s="3">
         <v>0</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="2">
-        <v>16</v>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>18</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
       </c>
       <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="2">
-        <v>17</v>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
       </c>
       <c r="C18" s="3">
         <v>0</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B19" s="2">
-        <v>18</v>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0</v>
       </c>
       <c r="C19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="2">
-        <v>19</v>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0</v>
       </c>
       <c r="C20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B21" s="2">
-        <v>20</v>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0</v>
       </c>
       <c r="C21" s="3">
         <v>0</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B22" s="2">
-        <v>21</v>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>23</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0</v>
       </c>
       <c r="C22" s="3">
         <v>0</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B23" s="2">
-        <v>22</v>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>24</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
       </c>
       <c r="C23" s="3">
         <v>0</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B24" s="2">
-        <v>23</v>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>25</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
       </c>
       <c r="C24" s="3">
         <v>0</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="2">
-        <v>24</v>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0</v>
       </c>
       <c r="C25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B26" s="2">
-        <v>25</v>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0</v>
       </c>
       <c r="C26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B27" s="2">
-        <v>26</v>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>28</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1</v>
       </c>
       <c r="C27" s="3">
         <v>0</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="2">
-        <v>27</v>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>29</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0</v>
       </c>
       <c r="C28" s="3">
         <v>0</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B29" s="2">
-        <v>28</v>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>30</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0</v>
       </c>
       <c r="C29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="2">
-        <v>29</v>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>31</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
       </c>
       <c r="C30" s="3">
         <v>0</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B31" s="2">
-        <v>30</v>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>32</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B32" s="2">
-        <v>31</v>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>33</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0</v>
       </c>
       <c r="C32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="2">
-        <v>32</v>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1</v>
       </c>
       <c r="C33" s="3">
         <v>0</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B34" s="2">
-        <v>33</v>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>35</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0</v>
       </c>
       <c r="C34" s="3">
         <v>0</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B35" s="2">
-        <v>34</v>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>36</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0</v>
       </c>
       <c r="C35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="2">
-        <v>35</v>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0</v>
       </c>
       <c r="C36" s="3">
         <v>0</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="2">
-        <v>36</v>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0</v>
       </c>
       <c r="C37" s="3">
         <v>0</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B38" s="2">
-        <v>37</v>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1</v>
       </c>
       <c r="C38" s="3">
         <v>0</v>
       </c>
-      <c r="D38" s="3"/>
+      <c r="D38" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="2">
-        <v>38</v>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1</v>
       </c>
       <c r="C39" s="3">
         <v>0</v>
       </c>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B40" s="2">
-        <v>39</v>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
+        <v>41</v>
+      </c>
+      <c r="B40" s="3">
+        <v>0</v>
       </c>
       <c r="C40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B41" s="2">
-        <v>40</v>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3">
+        <v>0</v>
       </c>
       <c r="C41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B42" s="2">
-        <v>41</v>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
+        <v>43</v>
+      </c>
+      <c r="B42" s="3">
+        <v>0</v>
       </c>
       <c r="C42" s="3">
         <v>0</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B43" s="2">
-        <v>42</v>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
+        <v>44</v>
+      </c>
+      <c r="B43" s="3">
+        <v>0</v>
       </c>
       <c r="C43" s="3">
         <v>0</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B44" s="2">
-        <v>43</v>
-      </c>
-      <c r="C44" s="3">
-        <v>0</v>
-      </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="2">
-        <v>44</v>
-      </c>
-      <c r="C45" s="3">
-        <v>0</v>
-      </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B46" s="2"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82AE40D-4653-447C-9679-4F72663E49E3}">
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.36328125" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="21"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="21"/>
+    </row>
+    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="12">
+        <v>3</v>
+      </c>
+      <c r="C3" s="13">
+        <v>0</v>
+      </c>
+      <c r="D3" s="13">
+        <v>1</v>
+      </c>
+      <c r="E3" s="19"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+    </row>
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="6">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="20"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+    </row>
+    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="6">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="20"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+    </row>
+    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="6">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="20"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+    </row>
+    <row r="7" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="6">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="20"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="6">
+        <v>12</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="6">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="21"/>
+    </row>
+    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="6">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="6">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="6">
+        <v>22</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="6">
+        <v>23</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="6">
+        <v>26</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="6">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="6">
+        <v>29</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="6">
+        <v>30</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="6">
+        <v>32</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="6">
+        <v>33</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="6">
+        <v>35</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="6">
+        <v>36</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="6">
+        <v>37</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="6">
+        <v>38</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="8">
+        <v>41</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="6">
+        <v>42</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="6">
+        <v>43</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="2"/>
+      <c r="B27" s="9">
+        <v>44</v>
+      </c>
+      <c r="C27" s="10">
+        <v>0</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E3:E27">
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula xml:space="preserve"> $D3 = 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H27">
+    <cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="1: BIDS">
+      <formula>NOT(ISERROR(SEARCH("1: BIDS",H3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="2: manual config">
+      <formula>NOT(ISERROR(SEARCH("2: manual config",H3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="3: preprocessed">
+      <formula>NOT(ISERROR(SEARCH("3: preprocessed",H3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{CDB9BFDA-ACFB-41B3-8FBF-60B598E357D1}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>1: BIDS," 2: manual config, 3: preprocessed"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"1: BIDS, 2: manual config, 3: preprocessed"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H27" xr:uid="{B8F1F2AB-BD36-452B-97E2-A1BEAE36882C}">
+      <formula1>"1: BIDS, 2: manual config, 3: preprocessed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{EC44A3D8-F782-4489-9D90-49570826E9F4}">
+            <xm:f>NOT(ISERROR(SEARCH($D3 = 1,E3)))</xm:f>
+            <xm:f>$D3 = 1</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E3:E27</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/scripts/eeg/subjects_processing_stage.xlsx
+++ b/scripts/eeg/subjects_processing_stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahm\projects\loc_analysis\scripts\eeg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD579A5-9A2E-47EA-8225-13E1F5897BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35183516-4460-4F25-80B9-6B21281410E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="12">
   <si>
     <t>sub</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>note</t>
-  </si>
-  <si>
-    <t>2: manual config</t>
   </si>
   <si>
     <t>process</t>
@@ -314,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -342,7 +339,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -360,131 +356,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -507,11 +386,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -529,63 +408,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1494,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82AE40D-4653-447C-9679-4F72663E49E3}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -1504,54 +1327,49 @@
     <col min="8" max="8" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="16" t="s">
+    <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="16" t="s">
+      <c r="D2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="16" t="s">
+      <c r="F2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="21"/>
-    </row>
-    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="12">
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="11">
         <v>3</v>
       </c>
-      <c r="C3" s="13">
-        <v>0</v>
-      </c>
-      <c r="D3" s="13">
-        <v>1</v>
-      </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-    </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="12">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12">
+        <v>1</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="6">
         <v>4</v>
       </c>
@@ -1561,17 +1379,14 @@
       <c r="D4" s="5">
         <v>1</v>
       </c>
-      <c r="E4" s="20"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="13"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-    </row>
-    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="6">
         <v>9</v>
       </c>
@@ -1581,17 +1396,14 @@
       <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="13"/>
+      <c r="G5" s="12"/>
       <c r="H5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-    </row>
-    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="6">
         <v>10</v>
       </c>
@@ -1601,17 +1413,14 @@
       <c r="D6" s="5">
         <v>1</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="19"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="13"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-    </row>
-    <row r="7" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="6">
         <v>11</v>
       </c>
@@ -1621,14 +1430,14 @@
       <c r="D7" s="5">
         <v>1</v>
       </c>
-      <c r="E7" s="20"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="13"/>
+      <c r="G7" s="12"/>
       <c r="H7" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="6">
         <v>12</v>
       </c>
@@ -1638,14 +1447,14 @@
       <c r="D8" s="5">
         <v>1</v>
       </c>
-      <c r="E8" s="20"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="13"/>
+      <c r="G8" s="12"/>
       <c r="H8" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="6">
         <v>17</v>
       </c>
@@ -1659,13 +1468,12 @@
         <v>0</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="13"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="21"/>
-    </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="6">
         <v>20</v>
       </c>
@@ -1679,16 +1487,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>12</v>
-      </c>
       <c r="H10" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="6">
         <v>21</v>
       </c>
@@ -1702,12 +1510,12 @@
         <v>0</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="13"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="6">
         <v>22</v>
       </c>
@@ -1721,12 +1529,12 @@
         <v>0</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="13"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="6">
         <v>23</v>
       </c>
@@ -1740,12 +1548,12 @@
         <v>0</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="13"/>
+      <c r="G13" s="12"/>
       <c r="H13" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="6">
         <v>26</v>
       </c>
@@ -1757,12 +1565,12 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="13"/>
+      <c r="G14" s="12"/>
       <c r="H14" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="6">
         <v>27</v>
       </c>
@@ -1774,12 +1582,12 @@
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="13"/>
+      <c r="G15" s="12"/>
       <c r="H15" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="6">
         <v>29</v>
       </c>
@@ -1791,7 +1599,7 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="13"/>
+      <c r="G16" s="12"/>
       <c r="H16" s="7" t="s">
         <v>7</v>
       </c>
@@ -1808,7 +1616,7 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="13"/>
+      <c r="G17" s="12"/>
       <c r="H17" s="7" t="s">
         <v>7</v>
       </c>
@@ -1825,7 +1633,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="13"/>
+      <c r="G18" s="12"/>
       <c r="H18" s="7" t="s">
         <v>7</v>
       </c>
@@ -1842,7 +1650,7 @@
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="13"/>
+      <c r="G19" s="12"/>
       <c r="H19" s="7" t="s">
         <v>7</v>
       </c>
@@ -1859,7 +1667,7 @@
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-      <c r="G20" s="13"/>
+      <c r="G20" s="12"/>
       <c r="H20" s="7" t="s">
         <v>7</v>
       </c>
@@ -1876,7 +1684,7 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="12"/>
       <c r="H21" s="7" t="s">
         <v>7</v>
       </c>
@@ -1893,7 +1701,7 @@
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-      <c r="G22" s="13"/>
+      <c r="G22" s="12"/>
       <c r="H22" s="7" t="s">
         <v>7</v>
       </c>
@@ -1910,7 +1718,7 @@
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="13"/>
+      <c r="G23" s="12"/>
       <c r="H23" s="7" t="s">
         <v>7</v>
       </c>
@@ -1927,7 +1735,7 @@
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="13"/>
+      <c r="G24" s="12"/>
       <c r="H24" s="7" t="s">
         <v>7</v>
       </c>
@@ -1944,7 +1752,7 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="13"/>
+      <c r="G25" s="12"/>
       <c r="H25" s="7" t="s">
         <v>7</v>
       </c>
@@ -1961,7 +1769,7 @@
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="13"/>
+      <c r="G26" s="12"/>
       <c r="H26" s="7" t="s">
         <v>7</v>
       </c>
@@ -1980,25 +1788,25 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="16" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E27">
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula xml:space="preserve"> $D3 = 1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H27">
-    <cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="1: BIDS">
-      <formula>NOT(ISERROR(SEARCH("1: BIDS",H3)))</formula>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="3: preprocessed">
+      <formula>NOT(ISERROR(SEARCH("3: preprocessed",H3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="2: manual config">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="2: manual config">
       <formula>NOT(ISERROR(SEARCH("2: manual config",H3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="3: preprocessed">
-      <formula>NOT(ISERROR(SEARCH("3: preprocessed",H3)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="1: BIDS">
+      <formula>NOT(ISERROR(SEARCH("1: BIDS",H3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">

--- a/scripts/eeg/subjects_processing_stage.xlsx
+++ b/scripts/eeg/subjects_processing_stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahm\projects\loc_analysis\scripts\eeg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35183516-4460-4F25-80B9-6B21281410E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85212E82-80D8-4E6E-9A26-DC5E5EF3CE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="17">
   <si>
     <t>sub</t>
   </si>
@@ -61,10 +61,25 @@
     <t>process</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>3: preprocessed</t>
+  </si>
+  <si>
+    <t>Lost many epochs (enc: 20, ret: 33)</t>
+  </si>
+  <si>
+    <t>2: manual config</t>
+  </si>
+  <si>
     <t>no</t>
   </si>
   <si>
-    <t>PSD plots very noisy</t>
+    <t>enc_start and first few trials were not recorded</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1338,7 @@
     <col min="2" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.36328125" customWidth="1"/>
+    <col min="7" max="7" width="29.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1449,7 +1464,9 @@
       </c>
       <c r="E8" s="19"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="12"/>
+      <c r="G8" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="H8" s="7" t="s">
         <v>7</v>
       </c>
@@ -1467,10 +1484,12 @@
       <c r="E9" s="5">
         <v>0</v>
       </c>
-      <c r="F9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G9" s="12"/>
       <c r="H9" s="7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1489,11 +1508,9 @@
       <c r="F10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>11</v>
-      </c>
+      <c r="G10" s="12"/>
       <c r="H10" s="7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1509,10 +1526,14 @@
       <c r="E11" s="5">
         <v>0</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="12"/>
+      <c r="F11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="H11" s="7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1528,10 +1549,12 @@
       <c r="E12" s="5">
         <v>0</v>
       </c>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G12" s="12"/>
       <c r="H12" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1547,10 +1570,12 @@
       <c r="E13" s="5">
         <v>0</v>
       </c>
-      <c r="F13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G13" s="12"/>
       <c r="H13" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1563,11 +1588,15 @@
       <c r="D14" s="5">
         <v>0</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G14" s="12"/>
       <c r="H14" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1580,11 +1609,15 @@
       <c r="D15" s="5">
         <v>0</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G15" s="12"/>
       <c r="H15" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1597,9 +1630,15 @@
       <c r="D16" s="5">
         <v>0</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="12"/>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="H16" s="7" t="s">
         <v>7</v>
       </c>
@@ -1614,11 +1653,15 @@
       <c r="D17" s="5">
         <v>0</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G17" s="12"/>
       <c r="H17" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1631,11 +1674,15 @@
       <c r="D18" s="5">
         <v>0</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G18" s="12"/>
       <c r="H18" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1648,11 +1695,15 @@
       <c r="D19" s="5">
         <v>0</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G19" s="12"/>
       <c r="H19" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/scripts/eeg/subjects_processing_stage.xlsx
+++ b/scripts/eeg/subjects_processing_stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahm\projects\loc_analysis\scripts\eeg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85212E82-80D8-4E6E-9A26-DC5E5EF3CE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B137AD0D-988D-4F21-96DA-4BB5493B5E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="18">
   <si>
     <t>sub</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>enc_start and first few trials were not recorded</t>
+  </si>
+  <si>
+    <t>Many frontal channels are noisy</t>
   </si>
 </sst>
 </file>
@@ -1716,11 +1719,15 @@
       <c r="D20" s="5">
         <v>0</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="E20" s="5">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G20" s="12"/>
       <c r="H20" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1733,11 +1740,15 @@
       <c r="D21" s="5">
         <v>0</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G21" s="12"/>
       <c r="H21" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1750,11 +1761,15 @@
       <c r="D22" s="5">
         <v>0</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G22" s="12"/>
       <c r="H22" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1767,11 +1782,15 @@
       <c r="D23" s="5">
         <v>0</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G23" s="12"/>
       <c r="H23" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1784,11 +1803,15 @@
       <c r="D24" s="4">
         <v>0</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="G24" s="12"/>
       <c r="H24" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1801,11 +1824,15 @@
       <c r="D25" s="5">
         <v>0</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G25" s="12"/>
       <c r="H25" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1818,11 +1845,17 @@
       <c r="D26" s="5">
         <v>0</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="12"/>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="H26" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1836,11 +1869,17 @@
       <c r="D27" s="10">
         <v>0</v>
       </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
+      <c r="E27" s="10">
+        <v>0</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>17</v>
+      </c>
       <c r="H27" s="16" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/eeg/subjects_processing_stage.xlsx
+++ b/scripts/eeg/subjects_processing_stage.xlsx
@@ -8,28 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahm\projects\loc_analysis\scripts\eeg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B137AD0D-988D-4F21-96DA-4BB5493B5E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8061DF27-3882-4BCF-8970-32A7B94D1DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all_subjects" sheetId="1" r:id="rId1"/>
     <sheet name="beh_incl_subjects" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">beh_incl_subjects!$A$1:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">beh_incl_subjects!$A$1:$G$31</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="16">
   <si>
     <t>sub</t>
   </si>
@@ -61,9 +72,6 @@
     <t>process</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -73,16 +81,13 @@
     <t>Lost many epochs (enc: 20, ret: 33)</t>
   </si>
   <si>
-    <t>2: manual config</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>enc_start and first few trials were not recorded</t>
   </si>
   <si>
     <t>Many frontal channels are noisy</t>
+  </si>
+  <si>
+    <t>Table. Subjects who did not fail behavioral exclusion criteria</t>
   </si>
 </sst>
 </file>
@@ -298,21 +303,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="mediumDashed">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="mediumDashed">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color theme="1"/>
@@ -325,11 +315,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="mediumDashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -366,8 +371,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -376,6 +380,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1335,95 +1345,87 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82AE40D-4653-447C-9679-4F72663E49E3}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.7265625" customWidth="1"/>
     <col min="8" max="8" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="D3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="11">
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="11">
         <v>3</v>
       </c>
-      <c r="C3" s="12">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12">
-        <v>1</v>
-      </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="13" t="s">
+      <c r="C4" s="12">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="12">
+        <v>0</v>
+      </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6">
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="6">
         <v>4</v>
       </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="6">
-        <v>9</v>
-      </c>
       <c r="C5" s="5">
         <v>0</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
       <c r="G5" s="12"/>
       <c r="H5" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="5">
         <v>0</v>
@@ -1431,16 +1433,18 @@
       <c r="D6" s="5">
         <v>1</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
       <c r="G6" s="12"/>
       <c r="H6" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
@@ -1448,16 +1452,18 @@
       <c r="D7" s="5">
         <v>1</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
       <c r="G7" s="12"/>
       <c r="H7" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5">
         <v>0</v>
@@ -1465,40 +1471,40 @@
       <c r="D8" s="5">
         <v>1</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="12" t="s">
-        <v>11</v>
-      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12"/>
       <c r="H8" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="6">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="18"/>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="6">
         <v>17</v>
       </c>
-      <c r="C9" s="5">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6">
-        <v>20</v>
-      </c>
       <c r="C10" s="5">
         <v>0</v>
       </c>
@@ -1508,62 +1514,62 @@
       <c r="E10" s="5">
         <v>0</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>10</v>
+      <c r="F10" s="5">
+        <v>1</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="6">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="6">
+        <v>21</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="6">
-        <v>21</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="6">
+      <c r="H12" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="6">
         <v>22</v>
       </c>
-      <c r="C12" s="5">
-        <v>0</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="6">
-        <v>23</v>
-      </c>
       <c r="C13" s="5">
         <v>0</v>
       </c>
@@ -1573,17 +1579,17 @@
       <c r="E13" s="5">
         <v>0</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>10</v>
+      <c r="F13" s="5">
+        <v>1</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="6">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
@@ -1594,17 +1600,17 @@
       <c r="E14" s="5">
         <v>0</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>10</v>
+      <c r="F14" s="5">
+        <v>1</v>
       </c>
       <c r="G14" s="12"/>
       <c r="H14" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
@@ -1615,17 +1621,17 @@
       <c r="E15" s="5">
         <v>0</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>10</v>
+      <c r="F15" s="5">
+        <v>1</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
@@ -1634,21 +1640,19 @@
         <v>0</v>
       </c>
       <c r="E16" s="5">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="12"/>
       <c r="H16" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
@@ -1657,19 +1661,21 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="H17" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C18" s="5">
         <v>0</v>
@@ -1680,17 +1686,17 @@
       <c r="E18" s="5">
         <v>0</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>10</v>
+      <c r="F18" s="5">
+        <v>1</v>
       </c>
       <c r="G18" s="12"/>
       <c r="H18" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="5">
         <v>0</v>
@@ -1701,17 +1707,17 @@
       <c r="E19" s="5">
         <v>0</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>10</v>
+      <c r="F19" s="5">
+        <v>1</v>
       </c>
       <c r="G19" s="12"/>
       <c r="H19" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C20" s="5">
         <v>0</v>
@@ -1722,17 +1728,17 @@
       <c r="E20" s="5">
         <v>0</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>10</v>
+      <c r="F20" s="5">
+        <v>1</v>
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="5">
         <v>0</v>
@@ -1743,17 +1749,17 @@
       <c r="E21" s="5">
         <v>0</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>10</v>
+      <c r="F21" s="5">
+        <v>1</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="5">
         <v>0</v>
@@ -1764,17 +1770,17 @@
       <c r="E22" s="5">
         <v>0</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>10</v>
+      <c r="F22" s="5">
+        <v>1</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="5">
         <v>0</v>
@@ -1785,122 +1791,149 @@
       <c r="E23" s="5">
         <v>0</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>10</v>
+      <c r="F23" s="5">
+        <v>1</v>
       </c>
       <c r="G23" s="12"/>
       <c r="H23" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="8">
-        <v>41</v>
-      </c>
-      <c r="C24" s="4">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>10</v>
+      <c r="B24" s="6">
+        <v>38</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="6">
-        <v>42</v>
-      </c>
-      <c r="C25" s="5">
-        <v>0</v>
-      </c>
-      <c r="D25" s="5">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>10</v>
+      <c r="B25" s="8">
+        <v>41</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="6">
+        <v>42</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5">
+        <v>1</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="6">
         <v>43</v>
       </c>
-      <c r="C26" s="5">
-        <v>0</v>
-      </c>
-      <c r="D26" s="5">
-        <v>0</v>
-      </c>
-      <c r="E26" s="5">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" s="7" t="s">
+      <c r="C27" s="5">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="2"/>
-      <c r="B27" s="9">
+      <c r="H27" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="2"/>
+      <c r="B28" s="9">
         <v>44</v>
       </c>
-      <c r="C27" s="10">
-        <v>0</v>
-      </c>
-      <c r="D27" s="10">
-        <v>0</v>
-      </c>
-      <c r="E27" s="10">
-        <v>0</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" s="16" t="s">
+      <c r="C28" s="10">
+        <v>0</v>
+      </c>
+      <c r="D28" s="10">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0</v>
+      </c>
+      <c r="F28" s="20">
+        <v>1</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>14</v>
       </c>
+      <c r="H28" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F30">
+        <f xml:space="preserve"> SUM($F4)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E3:E27">
+  <conditionalFormatting sqref="E4:E28">
     <cfRule type="expression" dxfId="4" priority="7">
-      <formula xml:space="preserve"> $D3 = 1</formula>
+      <formula xml:space="preserve"> $D4 = 1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H27">
+  <conditionalFormatting sqref="H4:H28">
     <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="3: preprocessed">
-      <formula>NOT(ISERROR(SEARCH("3: preprocessed",H3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("3: preprocessed",H4)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="2: manual config">
-      <formula>NOT(ISERROR(SEARCH("2: manual config",H3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("2: manual config",H4)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="1: BIDS">
-      <formula>NOT(ISERROR(SEARCH("1: BIDS",H3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("1: BIDS",H4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{CDB9BFDA-ACFB-41B3-8FBF-60B598E357D1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3" xr:uid="{CDB9BFDA-ACFB-41B3-8FBF-60B598E357D1}">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
           <x12ac:list>1: BIDS," 2: manual config, 3: preprocessed"</x12ac:list>
@@ -1910,18 +1943,19 @@
         </mc:Fallback>
       </mc:AlternateContent>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H27" xr:uid="{B8F1F2AB-BD36-452B-97E2-A1BEAE36882C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H28" xr:uid="{B8F1F2AB-BD36-452B-97E2-A1BEAE36882C}">
       <formula1>"1: BIDS, 2: manual config, 3: preprocessed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="8" operator="containsText" id="{EC44A3D8-F782-4489-9D90-49570826E9F4}">
-            <xm:f>NOT(ISERROR(SEARCH($D3 = 1,E3)))</xm:f>
-            <xm:f>$D3 = 1</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($D4 = 1,E4)))</xm:f>
+            <xm:f>$D4 = 1</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -1933,7 +1967,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E3:E27</xm:sqref>
+          <xm:sqref>E4:E28</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/scripts/eeg/subjects_processing_stage.xlsx
+++ b/scripts/eeg/subjects_processing_stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahm\projects\loc_analysis\scripts\eeg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DF0771-6D41-4070-BB8D-638EB37B366F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3E72B1-B07C-4376-927F-42DB1C6A4EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-27090" yWindow="1815" windowWidth="14400" windowHeight="7275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="eeg_analysis" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="15">
   <si>
     <t>sub</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Many frontal channels are noisy</t>
   </si>
   <si>
-    <t>Laura/Javier: Adjust data curation?</t>
-  </si>
-  <si>
     <t>enc_start and first trials were not recorded</t>
   </si>
   <si>
@@ -88,10 +85,7 @@
     <t>Subjects preprocessed:</t>
   </si>
   <si>
-    <t>Laura/Javier: Adjust data curation? Enc. Trial 13 missing</t>
-  </si>
-  <si>
-    <t>Laura/Javier: Adjust data curation? Enc. Trial 64 missing</t>
+    <t>BLOCKER: fix bug in behavioral data (missing enc trial)</t>
   </si>
 </sst>
 </file>
@@ -437,22 +431,7 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp"/>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -481,6 +460,11 @@
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp"/>
       </fill>
     </dxf>
   </dxfs>
@@ -780,7 +764,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -832,7 +816,7 @@
       </c>
       <c r="G6" s="13"/>
       <c r="I6" s="17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J6" s="20">
         <f>COUNTA(B5:B46)</f>
@@ -853,7 +837,7 @@
       </c>
       <c r="G7" s="13"/>
       <c r="I7" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J7" s="21">
         <f>COUNTIF(C:C, 0)</f>
@@ -874,7 +858,7 @@
       </c>
       <c r="G8" s="13"/>
       <c r="I8" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J8" s="22">
         <f>COUNTIF(F:F,"3: preprocessed")</f>
@@ -1078,7 +1062,7 @@
         <v>5</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1096,7 +1080,7 @@
         <v>5</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1114,7 +1098,7 @@
         <v>5</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1132,7 +1116,7 @@
         <v>5</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1150,7 +1134,7 @@
         <v>5</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1168,7 +1152,7 @@
         <v>5</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1188,7 +1172,7 @@
         <v>5</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1526,20 +1510,20 @@
       <sortCondition ref="F4"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="B5:G46">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$C5 = 1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F5:F46 I6:I8">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="3: preprocessed">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="3: preprocessed">
       <formula>NOT(ISERROR(SEARCH("3: preprocessed",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="2: manual config">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="2: manual config">
       <formula>NOT(ISERROR(SEARCH("2: manual config",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="1: BIDS">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="1: BIDS">
       <formula>NOT(ISERROR(SEARCH("1: BIDS",F5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:G46">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>$C5 = 1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">

--- a/scripts/eeg/subjects_processing_stage.xlsx
+++ b/scripts/eeg/subjects_processing_stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahm\projects\loc_analysis\scripts\eeg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3E72B1-B07C-4376-927F-42DB1C6A4EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4AA980-7DDB-4263-B595-2E1B8E3AC6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-27090" yWindow="1815" windowWidth="14400" windowHeight="7275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="eeg_analysis" sheetId="4" r:id="rId1"/>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="29" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" s="9">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C29" s="3">
         <v>0</v>
